--- a/diplom/excel/график_1_рынок.xlsx
+++ b/diplom/excel/график_1_рынок.xlsx
@@ -27,6 +27,7 @@
     </font>
     <font>
       <b val="1"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="3">
@@ -183,7 +184,10 @@
           </val>
         </ser>
         <dLbls>
+          <numFmt formatCode="0.0"/>
           <showVal val="1"/>
+          <showCatName val="0"/>
+          <showSerName val="0"/>
         </dLbls>
         <gapWidth val="150"/>
         <axId val="10"/>
@@ -195,23 +199,19 @@
           <orientation val="minMax"/>
         </scaling>
         <axPos val="l"/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Год</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <txPr>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="1100" b="0"/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
       </catAx>
@@ -231,14 +231,26 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>Объём рынка, млрд ₽</a:t>
+                  <a:t>млрд ₽</a:t>
                 </a:r>
               </a:p>
             </rich>
           </tx>
         </title>
+        <numFmt formatCode="0.0" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <txPr>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="1100" b="0"/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+          </a:p>
+        </txPr>
         <crossAx val="10"/>
       </valAx>
     </plotArea>
@@ -257,7 +269,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="7200000" cy="3960000"/>
+    <ext cx="6480000" cy="4320000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>

--- a/diplom/excel/график_1_рынок.xlsx
+++ b/diplom/excel/график_1_рынок.xlsx
@@ -27,6 +27,7 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
   </fonts>
@@ -39,7 +40,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9E1F2"/>
+        <fgColor rgb="004472C4"/>
       </patternFill>
     </fill>
   </fills>
@@ -138,7 +139,7 @@
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="11"/>
+  <style val="10"/>
   <chart>
     <title>
       <tx>
@@ -149,16 +150,15 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Динамика объёма рынка пожарной автоматики РФ, 2023–2026 гг.</a:t>
+              <a:t>Динамика объёма рынка пожарной автоматики РФ</a:t>
             </a:r>
           </a:p>
         </rich>
       </tx>
     </title>
     <plotArea>
-      <barChart>
-        <barDir val="col"/>
-        <grouping val="clustered"/>
+      <areaChart>
+        <grouping val="standard"/>
         <ser>
           <idx val="0"/>
           <order val="0"/>
@@ -168,6 +168,9 @@
             </strRef>
           </tx>
           <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="4472C4"/>
+            </a:solidFill>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
@@ -189,23 +192,24 @@
           <showCatName val="0"/>
           <showSerName val="0"/>
         </dLbls>
-        <gapWidth val="150"/>
         <axId val="10"/>
         <axId val="100"/>
-      </barChart>
+      </areaChart>
       <catAx>
         <axId val="10"/>
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
+        <numFmt formatCode="0" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <txPr>
           <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
           <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
-              <a:defRPr sz="1100" b="0"/>
+              <a:defRPr sz="1200" b="0"/>
             </a:pPr>
             <a:r>
               <a:t/>
@@ -220,8 +224,8 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
-        <majorGridlines/>
         <title>
           <tx>
             <rich>
@@ -244,7 +248,7 @@
           <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
           <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
-              <a:defRPr sz="1100" b="0"/>
+              <a:defRPr sz="1200" b="0"/>
             </a:pPr>
             <a:r>
               <a:t/>
@@ -269,7 +273,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6480000" cy="4320000"/>
+    <ext cx="6840000" cy="4680000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -579,7 +583,7 @@
   <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -596,40 +600,32 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
+      <c r="A2" t="n">
+        <v>2023</v>
       </c>
       <c r="B2" t="n">
         <v>45.8</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
+      <c r="A3" t="n">
+        <v>2024</v>
       </c>
       <c r="B3" t="n">
         <v>49.1</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+      <c r="A4" t="n">
+        <v>2025</v>
       </c>
       <c r="B4" t="n">
         <v>54</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026 (прогноз)</t>
-        </is>
+      <c r="A5" t="n">
+        <v>2026</v>
       </c>
       <c r="B5" t="n">
         <v>58.8</v>
